--- a/app/reports/FTHY_research.xlsx
+++ b/app/reports/FTHY_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>12.6</v>
+        <v>12.625</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.837</v>
+        <v>0.835</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05217999935150146</v>
+        <v>0.05341000080108643</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>36772987.93650794</v>
+        <v>36772988.1980198</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>12.6</v>
+        <v>12.625</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>463339648</v>
+        <v>464258976</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>18.26</v>
+        <v>18.3</v>
       </c>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C6" s="32" t="n"/>
       <c r="D6" s="33" t="n">
-        <v>11.976446</v>
+        <v>12.186379</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>501906880</v>
+        <v>520056576</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>8.991935</v>
+        <v>9.317097</v>
       </c>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="33" t="n">
-        <v>47.549</v>
+        <v>49.538</v>
       </c>
     </row>
     <row r="9">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C9" s="32" t="n"/>
       <c r="D9" s="33" t="n">
-        <v>19.536882</v>
+        <v>19.75276</v>
       </c>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C10" s="32" t="n"/>
       <c r="D10" s="33" t="n">
-        <v>19.541725</v>
+        <v>19.759157</v>
       </c>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>19.306181</v>
+        <v>19.7072</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1640,14 +1640,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>729146688</v>
+        <v>739172160</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>1.9058074</v>
+        <v>1.9320114</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>147.612</v>
+        <v>149.3</v>
       </c>
     </row>
     <row r="13">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C13" s="32" t="n"/>
       <c r="D13" s="33" t="n">
-        <v>18.35459</v>
+        <v>18.364042</v>
       </c>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n"/>
